--- a/Renda_por_Secao_CNAE_RAIS_Capanema.xlsx
+++ b/Renda_por_Secao_CNAE_RAIS_Capanema.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -448,600 +448,569 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Seção</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Nome Seção</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Renda Média Capanema (R$)</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Vínculos Capanema</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Renda Média Pará (R$)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Vínculos Pará</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>QL Renda (Cap/Pa)</t>
         </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>2949.361503</v>
-      </c>
-      <c r="D4" t="n">
-        <v>1324</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2651.069507</v>
-      </c>
-      <c r="F4" t="n">
-        <v>112932</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.112518</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS EXTRATIVAS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>2949.361503</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1324</v>
       </c>
       <c r="E5" t="n">
-        <v>7137.263608</v>
+        <v>2651.069507</v>
       </c>
       <c r="F5" t="n">
-        <v>33494</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>112932</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.112518</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2180.908383</v>
+          <t>INDÚSTRIAS EXTRATIVAS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>433</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3300.425824</v>
+        <v>7137.263608</v>
       </c>
       <c r="F6" t="n">
-        <v>309524</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.6607960000000001</v>
+        <v>33494</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ELETRICIDADE E GÁS</t>
+          <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5793.77</v>
+        <v>2180.908383</v>
       </c>
       <c r="D7" t="n">
-        <v>4</v>
+        <v>433</v>
       </c>
       <c r="E7" t="n">
-        <v>6811.088797</v>
+        <v>3300.425824</v>
       </c>
       <c r="F7" t="n">
-        <v>12905</v>
+        <v>309524</v>
       </c>
       <c r="G7" t="n">
-        <v>0.850638</v>
+        <v>0.6607960000000001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
+          <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5629.5325</v>
+        <v>5793.77</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>3694.276637</v>
+        <v>6811.088797</v>
       </c>
       <c r="F8" t="n">
-        <v>21898</v>
+        <v>12905</v>
       </c>
       <c r="G8" t="n">
-        <v>1.523852</v>
+        <v>0.850638</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CONSTRUÇÃO</t>
+          <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2296.320405</v>
+        <v>5629.5325</v>
       </c>
       <c r="D9" t="n">
-        <v>74</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>2999.876325</v>
+        <v>3694.276637</v>
       </c>
       <c r="F9" t="n">
-        <v>157501</v>
+        <v>21898</v>
       </c>
       <c r="G9" t="n">
-        <v>0.765472</v>
+        <v>1.523852</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
+          <t>CONSTRUÇÃO</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2146.526948</v>
+        <v>2296.320405</v>
       </c>
       <c r="D10" t="n">
-        <v>1517</v>
+        <v>74</v>
       </c>
       <c r="E10" t="n">
-        <v>2432.95962</v>
+        <v>2999.876325</v>
       </c>
       <c r="F10" t="n">
-        <v>608892</v>
+        <v>157501</v>
       </c>
       <c r="G10" t="n">
-        <v>0.88227</v>
+        <v>0.765472</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>G</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
+          <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2690.066898</v>
+        <v>2146.526948</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>1517</v>
       </c>
       <c r="E11" t="n">
-        <v>3339.776382</v>
+        <v>2432.95962</v>
       </c>
       <c r="F11" t="n">
-        <v>128222</v>
+        <v>608892</v>
       </c>
       <c r="G11" t="n">
-        <v>0.805463</v>
+        <v>0.88227</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ALOJAMENTO E ALIMENTAÇÃO</t>
+          <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1753.654231</v>
+        <v>2690.066898</v>
       </c>
       <c r="D12" t="n">
-        <v>78</v>
+        <v>245</v>
       </c>
       <c r="E12" t="n">
-        <v>1973.069964</v>
+        <v>3339.776382</v>
       </c>
       <c r="F12" t="n">
-        <v>91914</v>
+        <v>128222</v>
       </c>
       <c r="G12" t="n">
-        <v>0.888795</v>
+        <v>0.805463</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
+          <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2484.713214</v>
+        <v>1753.654231</v>
       </c>
       <c r="D13" t="n">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="E13" t="n">
-        <v>3129.720999</v>
+        <v>1973.069964</v>
       </c>
       <c r="F13" t="n">
-        <v>38111</v>
+        <v>91914</v>
       </c>
       <c r="G13" t="n">
-        <v>0.793909</v>
+        <v>0.888795</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>J</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
+          <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7755.840909</v>
+        <v>2484.713214</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="E14" t="n">
-        <v>8023.742075</v>
+        <v>3129.720999</v>
       </c>
       <c r="F14" t="n">
-        <v>36064</v>
+        <v>38111</v>
       </c>
       <c r="G14" t="n">
-        <v>0.966611</v>
+        <v>0.793909</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ATIVIDADES IMOBILIÁRIAS</t>
+          <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1773.17</v>
+        <v>7755.840909</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="E15" t="n">
-        <v>2585.215417</v>
+        <v>8023.742075</v>
       </c>
       <c r="F15" t="n">
-        <v>6664</v>
+        <v>36064</v>
       </c>
       <c r="G15" t="n">
-        <v>0.685889</v>
+        <v>0.966611</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>L</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
+          <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2162.836837</v>
+        <v>1773.17</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
-        <v>3829.814193</v>
+        <v>2585.215417</v>
       </c>
       <c r="F16" t="n">
-        <v>75357</v>
+        <v>6664</v>
       </c>
       <c r="G16" t="n">
-        <v>0.564737</v>
+        <v>0.685889</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
+          <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2081.546923</v>
+        <v>2162.836837</v>
       </c>
       <c r="D17" t="n">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="E17" t="n">
-        <v>2287.206213</v>
+        <v>3829.814193</v>
       </c>
       <c r="F17" t="n">
-        <v>288522</v>
+        <v>75357</v>
       </c>
       <c r="G17" t="n">
-        <v>0.910083</v>
+        <v>0.564737</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
+          <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>4569.475729</v>
+        <v>2081.546923</v>
       </c>
       <c r="D18" t="n">
-        <v>1585</v>
+        <v>143</v>
       </c>
       <c r="E18" t="n">
-        <v>5903.351765</v>
+        <v>2287.206213</v>
       </c>
       <c r="F18" t="n">
-        <v>1036043</v>
+        <v>288522</v>
       </c>
       <c r="G18" t="n">
-        <v>0.774048</v>
+        <v>0.910083</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>O</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EDUCAÇÃO</t>
+          <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1642.880297</v>
+        <v>4569.475729</v>
       </c>
       <c r="D19" t="n">
-        <v>101</v>
+        <v>1585</v>
       </c>
       <c r="E19" t="n">
-        <v>5355.117204</v>
+        <v>5903.351765</v>
       </c>
       <c r="F19" t="n">
-        <v>165960</v>
+        <v>1036043</v>
       </c>
       <c r="G19" t="n">
-        <v>0.306787</v>
+        <v>0.774048</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Q</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
+          <t>EDUCAÇÃO</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1578.647174</v>
+        <v>1642.880297</v>
       </c>
       <c r="D20" t="n">
-        <v>46</v>
+        <v>101</v>
       </c>
       <c r="E20" t="n">
-        <v>3644.708115</v>
+        <v>5355.117204</v>
       </c>
       <c r="F20" t="n">
-        <v>153167</v>
+        <v>165960</v>
       </c>
       <c r="G20" t="n">
-        <v>0.433134</v>
+        <v>0.306787</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>Q</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
+          <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1626.3675</v>
+        <v>1578.647174</v>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="E21" t="n">
-        <v>2525.133969</v>
+        <v>3644.708115</v>
       </c>
       <c r="F21" t="n">
-        <v>15126</v>
+        <v>153167</v>
       </c>
       <c r="G21" t="n">
-        <v>0.644072</v>
+        <v>0.433134</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
+          <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2018.154091</v>
+        <v>1626.3675</v>
       </c>
       <c r="D22" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>2675.306805</v>
+        <v>2525.133969</v>
       </c>
       <c r="F22" t="n">
-        <v>51761</v>
+        <v>15126</v>
       </c>
       <c r="G22" t="n">
-        <v>0.754364</v>
+        <v>0.644072</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SERVIÇOS DOMÉSTICOS</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2018.154091</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E23" t="n">
-        <v>1765.473529</v>
+        <v>2675.306805</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+        <v>51761</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.754364</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
+          <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1053,12 +1022,43 @@
         <v>0</v>
       </c>
       <c r="E24" t="n">
+        <v>1765.473529</v>
+      </c>
+      <c r="F24" t="n">
+        <v>17</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
         <v>6810.10122</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F25" t="n">
         <v>41</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/Renda_por_Secao_CNAE_RAIS_Capanema.xlsx
+++ b/Renda_por_Secao_CNAE_RAIS_Capanema.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,13 +32,47 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E2A5E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E2A5E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F4F4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -53,10 +87,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,646 +468,651 @@
   <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>RENDA MÉDIA POR SEÇÃO CNAE (RAIS 2025) — CAPANEMA vs PARÁ</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Vínculos ativos em 31/12, remuneração média nominal do ano (Vl Rem Média Nom). QL Renda = renda Capanema / renda Pará.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="3"/>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Seção</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Nome Seção</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Renda Média Capanema (R$)</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Vínculos Capanema</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Renda Média Pará (R$)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Vínculos Pará</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>QL Renda (Cap/Pa)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>AGRICULTURA, PECUÁRIA, PRODUÇÃO FLORESTAL, PESCA E AQÜICULTURA</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="7" t="n">
         <v>2949.361503</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="7" t="n">
         <v>1324</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="7" t="n">
         <v>2651.069507</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>112932</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5" s="7" t="n">
         <v>1.112518</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="8" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>INDÚSTRIAS EXTRATIVAS</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="9" t="n">
         <v>7137.263608</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="9" t="n">
         <v>33494</v>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>INDÚSTRIAS DE TRANSFORMAÇÃO</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="7" t="n">
         <v>2180.908383</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="7" t="n">
         <v>433</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" s="7" t="n">
         <v>3300.425824</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>309524</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="7" t="n">
         <v>0.6607960000000001</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="8" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>ELETRICIDADE E GÁS</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="9" t="n">
         <v>5793.77</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" s="9" t="n">
         <v>6811.088797</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="9" t="n">
         <v>12905</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8" s="9" t="n">
         <v>0.850638</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>ÁGUA, ESGOTO, ATIVIDADES DE GESTÃO DE RESÍDUOS E DESCONTAMINAÇÃO</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="7" t="n">
         <v>5629.5325</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="7" t="n">
         <v>3694.276637</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>21898</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9" s="7" t="n">
         <v>1.523852</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>F</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>CONSTRUÇÃO</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="9" t="n">
         <v>2296.320405</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="9" t="n">
         <v>74</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="9" t="n">
         <v>2999.876325</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="9" t="n">
         <v>157501</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10" s="9" t="n">
         <v>0.765472</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>G</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>COMÉRCIO; REPARAÇÃO DE VEÍCULOS AUTOMOTORES E MOTOCICLETAS</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="7" t="n">
         <v>2146.526948</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>1517</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="7" t="n">
         <v>2432.95962</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>608892</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11" s="7" t="n">
         <v>0.88227</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>TRANSPORTE, ARMAZENAGEM E CORREIO</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="9" t="n">
         <v>2690.066898</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="9" t="n">
         <v>245</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="9" t="n">
         <v>3339.776382</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="9" t="n">
         <v>128222</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12" s="9" t="n">
         <v>0.805463</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>ALOJAMENTO E ALIMENTAÇÃO</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="7" t="n">
         <v>1753.654231</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="7" t="n">
         <v>78</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" s="7" t="n">
         <v>1973.069964</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13" s="7" t="n">
         <v>91914</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13" s="7" t="n">
         <v>0.888795</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>J</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>INFORMAÇÃO E COMUNICAÇÃO</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="C14" s="9" t="n">
         <v>2484.713214</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14" s="9" t="n">
         <v>28</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" s="9" t="n">
         <v>3129.720999</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14" s="9" t="n">
         <v>38111</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14" s="9" t="n">
         <v>0.793909</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>K</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES FINANCEIRAS, DE SEGUROS E SERVIÇOS RELACIONADOS</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="C15" s="7" t="n">
         <v>7755.840909</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15" s="7" t="n">
         <v>77</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" s="7" t="n">
         <v>8023.742075</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15" s="7" t="n">
         <v>36064</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15" s="7" t="n">
         <v>0.966611</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES IMOBILIÁRIAS</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="C16" s="9" t="n">
         <v>1773.17</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="9" t="n">
         <v>2585.215417</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="9" t="n">
         <v>6664</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16" s="9" t="n">
         <v>0.685889</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>ATIVIDADES PROFISSIONAIS, CIENTÍFICAS E TÉCNICAS</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" s="7" t="n">
         <v>2162.836837</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17" s="7" t="n">
         <v>98</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17" s="7" t="n">
         <v>3829.814193</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="7" t="n">
         <v>75357</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17" s="7" t="n">
         <v>0.564737</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>ATIVIDADES ADMINISTRATIVAS E SERVIÇOS COMPLEMENTARES</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="9" t="n">
         <v>2081.546923</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18" s="9" t="n">
         <v>143</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18" s="9" t="n">
         <v>2287.206213</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18" s="9" t="n">
         <v>288522</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" s="9" t="n">
         <v>0.910083</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>ADMINISTRAÇÃO PÚBLICA, DEFESA E SEGURIDADE SOCIAL</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="C19" s="7" t="n">
         <v>4569.475729</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19" s="7" t="n">
         <v>1585</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="7" t="n">
         <v>5903.351765</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19" s="7" t="n">
         <v>1036043</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G19" s="7" t="n">
         <v>0.774048</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>EDUCAÇÃO</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="9" t="n">
         <v>1642.880297</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20" s="9" t="n">
         <v>101</v>
       </c>
-      <c r="E20" t="n">
+      <c r="E20" s="9" t="n">
         <v>5355.117204</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20" s="9" t="n">
         <v>165960</v>
       </c>
-      <c r="G20" t="n">
+      <c r="G20" s="9" t="n">
         <v>0.306787</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Q</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>SAÚDE HUMANA E SERVIÇOS SOCIAIS</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="C21" s="7" t="n">
         <v>1578.647174</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" s="7" t="n">
         <v>3644.708115</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="7" t="n">
         <v>153167</v>
       </c>
-      <c r="G21" t="n">
+      <c r="G21" s="7" t="n">
         <v>0.433134</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>ARTES, CULTURA, ESPORTE E RECREAÇÃO</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="9" t="n">
         <v>1626.3675</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22" s="9" t="n">
         <v>16</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="9" t="n">
         <v>2525.133969</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="9" t="n">
         <v>15126</v>
       </c>
-      <c r="G22" t="n">
+      <c r="G22" s="9" t="n">
         <v>0.644072</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>OUTRAS ATIVIDADES DE SERVIÇOS</t>
         </is>
       </c>
-      <c r="C23" t="n">
+      <c r="C23" s="7" t="n">
         <v>2018.154091</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="E23" t="n">
+      <c r="E23" s="7" t="n">
         <v>2675.306805</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23" s="7" t="n">
         <v>51761</v>
       </c>
-      <c r="G23" t="n">
+      <c r="G23" s="7" t="n">
         <v>0.754364</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>SERVIÇOS DOMÉSTICOS</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D24" t="n">
+      <c r="D24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24" s="9" t="n">
         <v>1765.473529</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24" s="9" t="n">
         <v>17</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>U</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>ORGANISMOS INTERNACIONAIS E OUTRAS INSTITUIÇÕES EXTRATERRITORIAIS</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D25" t="n">
+      <c r="D25" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" s="7" t="n">
         <v>6810.10122</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25" s="7" t="n">
         <v>41</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>